--- a/app/templates_excel/nigredo/n7_planets_en.xlsx
+++ b/app/templates_excel/nigredo/n7_planets_en.xlsx
@@ -1312,10 +1312,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1572,10 +1568,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1700,10 +1692,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2464,10 +2452,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2544,10 +2528,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2568,10 +2548,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2617,6 +2593,30 @@
   </si>
   <si>
     <t>A professor peering over his glasses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3736,34 +3736,34 @@
     </row>
     <row r="39" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>31</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>410</v>
+        <v>734</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.4">
@@ -3811,7 +3811,7 @@
         <v>32</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.4">
@@ -3819,7 +3819,7 @@
         <v>33</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.4">
@@ -3827,7 +3827,7 @@
         <v>34</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.4">
@@ -3835,7 +3835,7 @@
         <v>35</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.4">
@@ -3843,7 +3843,7 @@
         <v>36</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.4">
@@ -3851,7 +3851,7 @@
         <v>37</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>38</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.4">
@@ -3867,7 +3867,7 @@
         <v>39</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.4">
@@ -3875,7 +3875,7 @@
         <v>40</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.4">
@@ -3883,7 +3883,7 @@
         <v>41</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.4">
@@ -3891,7 +3891,7 @@
         <v>42</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.4">
@@ -3899,7 +3899,7 @@
         <v>43</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.4">
@@ -3907,7 +3907,7 @@
         <v>44</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>45</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.4">
@@ -3923,7 +3923,7 @@
         <v>46</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.4">
@@ -3931,7 +3931,7 @@
         <v>47</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.4">
@@ -3939,7 +3939,7 @@
         <v>48</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.4">
@@ -3947,7 +3947,7 @@
         <v>49</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.4">
@@ -3955,7 +3955,7 @@
         <v>50</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.4">
@@ -3963,7 +3963,7 @@
         <v>51</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>52</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.4">
@@ -3979,7 +3979,7 @@
         <v>53</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.4">
@@ -3987,7 +3987,7 @@
         <v>54</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.4">
@@ -3995,7 +3995,7 @@
         <v>55</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.4">
@@ -4003,39 +4003,39 @@
         <v>56</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.4">
@@ -4043,7 +4043,7 @@
         <v>362</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.4">
@@ -4051,7 +4051,7 @@
         <v>363</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.4">
@@ -4059,7 +4059,7 @@
         <v>57</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.4">
@@ -4067,7 +4067,7 @@
         <v>58</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.4">
@@ -4075,7 +4075,7 @@
         <v>59</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>60</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.4">
@@ -4091,7 +4091,7 @@
         <v>61</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.4">
@@ -4099,7 +4099,7 @@
         <v>62</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.4">
@@ -4107,7 +4107,7 @@
         <v>63</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.4">
@@ -4115,7 +4115,7 @@
         <v>64</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.4">
@@ -4123,7 +4123,7 @@
         <v>65</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.4">
@@ -4131,7 +4131,7 @@
         <v>66</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>67</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.4">
@@ -4147,7 +4147,7 @@
         <v>68</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.4">
@@ -4155,7 +4155,7 @@
         <v>69</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.4">
@@ -4163,7 +4163,7 @@
         <v>70</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.4">
@@ -4171,7 +4171,7 @@
         <v>71</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.4">
@@ -4179,7 +4179,7 @@
         <v>72</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.4">
@@ -4187,7 +4187,7 @@
         <v>73</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>74</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.4">
@@ -4203,7 +4203,7 @@
         <v>75</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.4">
@@ -4211,7 +4211,7 @@
         <v>76</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.4">
@@ -4219,7 +4219,7 @@
         <v>77</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.4">
@@ -4227,7 +4227,7 @@
         <v>78</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.4">
@@ -4235,7 +4235,7 @@
         <v>79</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.4">
@@ -4243,7 +4243,7 @@
         <v>80</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>81</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.4">
@@ -4259,7 +4259,7 @@
         <v>82</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.4">
@@ -4267,7 +4267,7 @@
         <v>83</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.4">
@@ -4275,39 +4275,39 @@
         <v>84</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="101" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.4">
@@ -4315,7 +4315,7 @@
         <v>364</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.4">
@@ -4323,7 +4323,7 @@
         <v>85</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.4">
@@ -4331,7 +4331,7 @@
         <v>86</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.4">
@@ -4339,7 +4339,7 @@
         <v>87</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.4">
@@ -4347,7 +4347,7 @@
         <v>88</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.4">
@@ -4355,7 +4355,7 @@
         <v>89</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>90</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.4">
@@ -4371,7 +4371,7 @@
         <v>91</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.4">
@@ -4379,7 +4379,7 @@
         <v>92</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.4">
@@ -4387,7 +4387,7 @@
         <v>93</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.4">
@@ -4395,7 +4395,7 @@
         <v>94</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.4">
@@ -4403,7 +4403,7 @@
         <v>95</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>475</v>
+        <v>733</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.4">
@@ -4411,7 +4411,7 @@
         <v>96</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>97</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.4">
@@ -4427,7 +4427,7 @@
         <v>98</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.4">
@@ -4435,7 +4435,7 @@
         <v>99</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.4">
@@ -4443,7 +4443,7 @@
         <v>100</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.4">
@@ -4451,7 +4451,7 @@
         <v>101</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.4">
@@ -4459,7 +4459,7 @@
         <v>102</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.4">
@@ -4467,7 +4467,7 @@
         <v>103</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>104</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.4">
@@ -4483,7 +4483,7 @@
         <v>105</v>
       </c>
       <c r="L123" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.4">
@@ -4491,7 +4491,7 @@
         <v>106</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.4">
@@ -4499,7 +4499,7 @@
         <v>107</v>
       </c>
       <c r="L125" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.4">
@@ -4507,7 +4507,7 @@
         <v>108</v>
       </c>
       <c r="L126" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.4">
@@ -4515,7 +4515,7 @@
         <v>109</v>
       </c>
       <c r="L127" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.4">
@@ -4523,7 +4523,7 @@
         <v>110</v>
       </c>
       <c r="L128" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>111</v>
       </c>
       <c r="L129" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.4">
@@ -4539,7 +4539,7 @@
         <v>112</v>
       </c>
       <c r="L130" s="7" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.4">
@@ -4547,39 +4547,39 @@
         <v>113</v>
       </c>
       <c r="L131" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="132" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K132" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>365</v>
       </c>
       <c r="L133" s="7" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.4">
@@ -4595,7 +4595,7 @@
         <v>114</v>
       </c>
       <c r="L134" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.4">
@@ -4603,7 +4603,7 @@
         <v>115</v>
       </c>
       <c r="L135" s="7" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.4">
@@ -4611,7 +4611,7 @@
         <v>116</v>
       </c>
       <c r="L136" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.4">
@@ -4619,7 +4619,7 @@
         <v>117</v>
       </c>
       <c r="L137" s="7" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.4">
@@ -4627,7 +4627,7 @@
         <v>118</v>
       </c>
       <c r="L138" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.4">
@@ -4635,7 +4635,7 @@
         <v>119</v>
       </c>
       <c r="L139" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>120</v>
       </c>
       <c r="L140" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.4">
@@ -4651,7 +4651,7 @@
         <v>121</v>
       </c>
       <c r="L141" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.4">
@@ -4659,7 +4659,7 @@
         <v>122</v>
       </c>
       <c r="L142" s="7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.4">
@@ -4667,7 +4667,7 @@
         <v>123</v>
       </c>
       <c r="L143" s="7" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.4">
@@ -4675,7 +4675,7 @@
         <v>124</v>
       </c>
       <c r="L144" s="7" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.4">
@@ -4683,7 +4683,7 @@
         <v>125</v>
       </c>
       <c r="L145" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.4">
@@ -4691,7 +4691,7 @@
         <v>126</v>
       </c>
       <c r="L146" s="7" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>127</v>
       </c>
       <c r="L147" s="7" t="s">
-        <v>507</v>
+        <v>735</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.4">
@@ -4707,7 +4707,7 @@
         <v>128</v>
       </c>
       <c r="L148" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.4">
@@ -4715,7 +4715,7 @@
         <v>129</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.4">
@@ -4723,7 +4723,7 @@
         <v>130</v>
       </c>
       <c r="L150" s="7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.4">
@@ -4731,7 +4731,7 @@
         <v>131</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.4">
@@ -4739,7 +4739,7 @@
         <v>132</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.4">
@@ -4747,7 +4747,7 @@
         <v>133</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>134</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.4">
@@ -4763,7 +4763,7 @@
         <v>135</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.4">
@@ -4771,7 +4771,7 @@
         <v>136</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.4">
@@ -4779,7 +4779,7 @@
         <v>137</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.4">
@@ -4787,7 +4787,7 @@
         <v>138</v>
       </c>
       <c r="L158" s="7" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.4">
@@ -4795,7 +4795,7 @@
         <v>139</v>
       </c>
       <c r="L159" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.4">
@@ -4803,7 +4803,7 @@
         <v>140</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>141</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.4">
@@ -4819,39 +4819,39 @@
         <v>142</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="163" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K163" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.4">
@@ -4859,7 +4859,7 @@
         <v>366</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>367</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.4">
@@ -4875,7 +4875,7 @@
         <v>143</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.4">
@@ -4883,7 +4883,7 @@
         <v>144</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.4">
@@ -4891,7 +4891,7 @@
         <v>145</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.4">
@@ -4899,7 +4899,7 @@
         <v>146</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.4">
@@ -4907,7 +4907,7 @@
         <v>147</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.4">
@@ -4915,7 +4915,7 @@
         <v>148</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>149</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.4">
@@ -4931,7 +4931,7 @@
         <v>150</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.4">
@@ -4939,7 +4939,7 @@
         <v>151</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.4">
@@ -4947,7 +4947,7 @@
         <v>152</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.4">
@@ -4955,7 +4955,7 @@
         <v>153</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.4">
@@ -4963,7 +4963,7 @@
         <v>154</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.4">
@@ -4971,7 +4971,7 @@
         <v>155</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>156</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.4">
@@ -4987,7 +4987,7 @@
         <v>157</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.4">
@@ -4995,7 +4995,7 @@
         <v>158</v>
       </c>
       <c r="L181" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.4">
@@ -5003,7 +5003,7 @@
         <v>159</v>
       </c>
       <c r="L182" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.4">
@@ -5011,7 +5011,7 @@
         <v>160</v>
       </c>
       <c r="L183" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.4">
@@ -5019,7 +5019,7 @@
         <v>161</v>
       </c>
       <c r="L184" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.4">
@@ -5027,7 +5027,7 @@
         <v>162</v>
       </c>
       <c r="L185" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>163</v>
       </c>
       <c r="L186" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.4">
@@ -5043,7 +5043,7 @@
         <v>164</v>
       </c>
       <c r="L187" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.4">
@@ -5051,7 +5051,7 @@
         <v>165</v>
       </c>
       <c r="L188" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.4">
@@ -5059,7 +5059,7 @@
         <v>166</v>
       </c>
       <c r="L189" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.4">
@@ -5067,7 +5067,7 @@
         <v>167</v>
       </c>
       <c r="L190" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.4">
@@ -5075,7 +5075,7 @@
         <v>168</v>
       </c>
       <c r="L191" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.4">
@@ -5083,7 +5083,7 @@
         <v>169</v>
       </c>
       <c r="L192" s="7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.4">
@@ -5091,39 +5091,39 @@
         <v>170</v>
       </c>
       <c r="L193" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="194" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K194" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.4">
@@ -5131,7 +5131,7 @@
         <v>368</v>
       </c>
       <c r="L195" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.4">
@@ -5139,7 +5139,7 @@
         <v>171</v>
       </c>
       <c r="L196" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>172</v>
       </c>
       <c r="L197" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.4">
@@ -5155,7 +5155,7 @@
         <v>173</v>
       </c>
       <c r="L198" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.4">
@@ -5163,7 +5163,7 @@
         <v>174</v>
       </c>
       <c r="L199" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.4">
@@ -5171,7 +5171,7 @@
         <v>175</v>
       </c>
       <c r="L200" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.4">
@@ -5179,7 +5179,7 @@
         <v>176</v>
       </c>
       <c r="L201" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.4">
@@ -5187,7 +5187,7 @@
         <v>177</v>
       </c>
       <c r="L202" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.4">
@@ -5195,7 +5195,7 @@
         <v>178</v>
       </c>
       <c r="L203" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>179</v>
       </c>
       <c r="L204" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.4">
@@ -5211,7 +5211,7 @@
         <v>180</v>
       </c>
       <c r="L205" s="7" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.4">
@@ -5219,7 +5219,7 @@
         <v>181</v>
       </c>
       <c r="L206" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.4">
@@ -5227,7 +5227,7 @@
         <v>182</v>
       </c>
       <c r="L207" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.4">
@@ -5235,7 +5235,7 @@
         <v>183</v>
       </c>
       <c r="L208" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.4">
@@ -5243,7 +5243,7 @@
         <v>184</v>
       </c>
       <c r="L209" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.4">
@@ -5251,7 +5251,7 @@
         <v>185</v>
       </c>
       <c r="L210" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.4">
@@ -5259,7 +5259,7 @@
         <v>186</v>
       </c>
       <c r="L211" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.4">
@@ -5267,7 +5267,7 @@
         <v>187</v>
       </c>
       <c r="L212" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.4">
@@ -5275,7 +5275,7 @@
         <v>188</v>
       </c>
       <c r="L213" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.4">
@@ -5283,7 +5283,7 @@
         <v>189</v>
       </c>
       <c r="L214" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.4">
@@ -5291,7 +5291,7 @@
         <v>190</v>
       </c>
       <c r="L215" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.4">
@@ -5299,7 +5299,7 @@
         <v>191</v>
       </c>
       <c r="L216" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.4">
@@ -5307,7 +5307,7 @@
         <v>192</v>
       </c>
       <c r="L217" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.4">
@@ -5315,7 +5315,7 @@
         <v>193</v>
       </c>
       <c r="L218" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.4">
@@ -5323,7 +5323,7 @@
         <v>194</v>
       </c>
       <c r="L219" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.4">
@@ -5331,7 +5331,7 @@
         <v>195</v>
       </c>
       <c r="L220" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.4">
@@ -5339,7 +5339,7 @@
         <v>196</v>
       </c>
       <c r="L221" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.4">
@@ -5347,7 +5347,7 @@
         <v>197</v>
       </c>
       <c r="L222" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.4">
@@ -5355,7 +5355,7 @@
         <v>198</v>
       </c>
       <c r="L223" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.4">
@@ -5363,39 +5363,39 @@
         <v>199</v>
       </c>
       <c r="L224" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="225" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K225" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.4">
@@ -5403,7 +5403,7 @@
         <v>369</v>
       </c>
       <c r="L226" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.4">
@@ -5411,7 +5411,7 @@
         <v>200</v>
       </c>
       <c r="L227" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.4">
@@ -5419,7 +5419,7 @@
         <v>201</v>
       </c>
       <c r="L228" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.4">
@@ -5427,7 +5427,7 @@
         <v>202</v>
       </c>
       <c r="L229" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.4">
@@ -5435,7 +5435,7 @@
         <v>203</v>
       </c>
       <c r="L230" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.4">
@@ -5443,7 +5443,7 @@
         <v>204</v>
       </c>
       <c r="L231" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.4">
@@ -5451,7 +5451,7 @@
         <v>205</v>
       </c>
       <c r="L232" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.4">
@@ -5459,7 +5459,7 @@
         <v>206</v>
       </c>
       <c r="L233" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.4">
@@ -5467,7 +5467,7 @@
         <v>207</v>
       </c>
       <c r="L234" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.4">
@@ -5475,7 +5475,7 @@
         <v>208</v>
       </c>
       <c r="L235" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.4">
@@ -5483,7 +5483,7 @@
         <v>209</v>
       </c>
       <c r="L236" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.4">
@@ -5491,7 +5491,7 @@
         <v>210</v>
       </c>
       <c r="L237" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.4">
@@ -5499,7 +5499,7 @@
         <v>211</v>
       </c>
       <c r="L238" s="7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.4">
@@ -5507,7 +5507,7 @@
         <v>212</v>
       </c>
       <c r="L239" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.4">
@@ -5515,7 +5515,7 @@
         <v>213</v>
       </c>
       <c r="L240" s="7" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.4">
@@ -5523,7 +5523,7 @@
         <v>214</v>
       </c>
       <c r="L241" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.4">
@@ -5531,7 +5531,7 @@
         <v>215</v>
       </c>
       <c r="L242" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.4">
@@ -5539,7 +5539,7 @@
         <v>216</v>
       </c>
       <c r="L243" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.4">
@@ -5547,7 +5547,7 @@
         <v>217</v>
       </c>
       <c r="L244" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.4">
@@ -5555,7 +5555,7 @@
         <v>218</v>
       </c>
       <c r="L245" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.4">
@@ -5563,7 +5563,7 @@
         <v>219</v>
       </c>
       <c r="L246" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.4">
@@ -5571,7 +5571,7 @@
         <v>220</v>
       </c>
       <c r="L247" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.4">
@@ -5579,7 +5579,7 @@
         <v>221</v>
       </c>
       <c r="L248" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.4">
@@ -5587,7 +5587,7 @@
         <v>222</v>
       </c>
       <c r="L249" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.4">
@@ -5595,7 +5595,7 @@
         <v>223</v>
       </c>
       <c r="L250" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.4">
@@ -5603,7 +5603,7 @@
         <v>224</v>
       </c>
       <c r="L251" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.4">
@@ -5611,7 +5611,7 @@
         <v>225</v>
       </c>
       <c r="L252" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.4">
@@ -5619,7 +5619,7 @@
         <v>226</v>
       </c>
       <c r="L253" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.4">
@@ -5627,7 +5627,7 @@
         <v>227</v>
       </c>
       <c r="L254" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.4">
@@ -5635,39 +5635,39 @@
         <v>228</v>
       </c>
       <c r="L255" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="256" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K256" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.4">
@@ -5675,7 +5675,7 @@
         <v>370</v>
       </c>
       <c r="L257" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.4">
@@ -5683,7 +5683,7 @@
         <v>229</v>
       </c>
       <c r="L258" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.4">
@@ -5691,7 +5691,7 @@
         <v>230</v>
       </c>
       <c r="L259" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.4">
@@ -5699,7 +5699,7 @@
         <v>231</v>
       </c>
       <c r="L260" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.4">
@@ -5707,7 +5707,7 @@
         <v>232</v>
       </c>
       <c r="L261" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.4">
@@ -5715,7 +5715,7 @@
         <v>233</v>
       </c>
       <c r="L262" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.4">
@@ -5723,7 +5723,7 @@
         <v>234</v>
       </c>
       <c r="L263" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.4">
@@ -5731,7 +5731,7 @@
         <v>235</v>
       </c>
       <c r="L264" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.4">
@@ -5739,7 +5739,7 @@
         <v>236</v>
       </c>
       <c r="L265" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.4">
@@ -5747,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.4">
@@ -5755,7 +5755,7 @@
         <v>237</v>
       </c>
       <c r="L267" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.4">
@@ -5763,7 +5763,7 @@
         <v>238</v>
       </c>
       <c r="L268" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.4">
@@ -5771,7 +5771,7 @@
         <v>239</v>
       </c>
       <c r="L269" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.4">
@@ -5779,7 +5779,7 @@
         <v>240</v>
       </c>
       <c r="L270" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.4">
@@ -5787,7 +5787,7 @@
         <v>241</v>
       </c>
       <c r="L271" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.4">
@@ -5795,7 +5795,7 @@
         <v>242</v>
       </c>
       <c r="L272" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.4">
@@ -5803,7 +5803,7 @@
         <v>243</v>
       </c>
       <c r="L273" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.4">
@@ -5811,7 +5811,7 @@
         <v>244</v>
       </c>
       <c r="L274" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.4">
@@ -5819,7 +5819,7 @@
         <v>245</v>
       </c>
       <c r="L275" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.4">
@@ -5827,7 +5827,7 @@
         <v>246</v>
       </c>
       <c r="L276" s="7" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.4">
@@ -5835,7 +5835,7 @@
         <v>247</v>
       </c>
       <c r="L277" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.4">
@@ -5843,7 +5843,7 @@
         <v>248</v>
       </c>
       <c r="L278" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.4">
@@ -5851,7 +5851,7 @@
         <v>249</v>
       </c>
       <c r="L279" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.4">
@@ -5859,7 +5859,7 @@
         <v>250</v>
       </c>
       <c r="L280" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.4">
@@ -5867,7 +5867,7 @@
         <v>251</v>
       </c>
       <c r="L281" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.4">
@@ -5875,7 +5875,7 @@
         <v>252</v>
       </c>
       <c r="L282" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.4">
@@ -5883,7 +5883,7 @@
         <v>253</v>
       </c>
       <c r="L283" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.4">
@@ -5891,7 +5891,7 @@
         <v>254</v>
       </c>
       <c r="L284" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.4">
@@ -5899,7 +5899,7 @@
         <v>255</v>
       </c>
       <c r="L285" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.4">
@@ -5907,39 +5907,39 @@
         <v>256</v>
       </c>
       <c r="L286" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="287" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K287" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.4">
@@ -5947,7 +5947,7 @@
         <v>371</v>
       </c>
       <c r="L288" s="7" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.4">
@@ -5955,7 +5955,7 @@
         <v>257</v>
       </c>
       <c r="L289" s="7" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.4">
@@ -5963,7 +5963,7 @@
         <v>258</v>
       </c>
       <c r="L290" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.4">
@@ -5971,7 +5971,7 @@
         <v>259</v>
       </c>
       <c r="L291" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.4">
@@ -5979,7 +5979,7 @@
         <v>260</v>
       </c>
       <c r="L292" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.4">
@@ -5987,7 +5987,7 @@
         <v>261</v>
       </c>
       <c r="L293" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.4">
@@ -5995,7 +5995,7 @@
         <v>262</v>
       </c>
       <c r="L294" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.4">
@@ -6003,7 +6003,7 @@
         <v>263</v>
       </c>
       <c r="L295" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.4">
@@ -6011,7 +6011,7 @@
         <v>264</v>
       </c>
       <c r="L296" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.4">
@@ -6019,7 +6019,7 @@
         <v>265</v>
       </c>
       <c r="L297" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.4">
@@ -6027,7 +6027,7 @@
         <v>266</v>
       </c>
       <c r="L298" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.4">
@@ -6035,7 +6035,7 @@
         <v>267</v>
       </c>
       <c r="L299" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.4">
@@ -6043,7 +6043,7 @@
         <v>268</v>
       </c>
       <c r="L300" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.4">
@@ -6051,7 +6051,7 @@
         <v>269</v>
       </c>
       <c r="L301" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.4">
@@ -6059,7 +6059,7 @@
         <v>270</v>
       </c>
       <c r="L302" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.4">
@@ -6067,7 +6067,7 @@
         <v>271</v>
       </c>
       <c r="L303" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.4">
@@ -6075,7 +6075,7 @@
         <v>272</v>
       </c>
       <c r="L304" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.4">
@@ -6083,7 +6083,7 @@
         <v>273</v>
       </c>
       <c r="L305" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.4">
@@ -6091,7 +6091,7 @@
         <v>274</v>
       </c>
       <c r="L306" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.4">
@@ -6099,7 +6099,7 @@
         <v>275</v>
       </c>
       <c r="L307" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.4">
@@ -6107,7 +6107,7 @@
         <v>276</v>
       </c>
       <c r="L308" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.4">
@@ -6115,7 +6115,7 @@
         <v>277</v>
       </c>
       <c r="L309" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.4">
@@ -6123,7 +6123,7 @@
         <v>278</v>
       </c>
       <c r="L310" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.4">
@@ -6131,7 +6131,7 @@
         <v>279</v>
       </c>
       <c r="L311" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.4">
@@ -6139,7 +6139,7 @@
         <v>280</v>
       </c>
       <c r="L312" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.4">
@@ -6147,7 +6147,7 @@
         <v>281</v>
       </c>
       <c r="L313" s="7" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.4">
@@ -6155,7 +6155,7 @@
         <v>282</v>
       </c>
       <c r="L314" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.4">
@@ -6163,7 +6163,7 @@
         <v>283</v>
       </c>
       <c r="L315" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.4">
@@ -6171,7 +6171,7 @@
         <v>284</v>
       </c>
       <c r="L316" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.4">
@@ -6179,39 +6179,39 @@
         <v>285</v>
       </c>
       <c r="L317" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="318" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K318" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.4">
@@ -6219,7 +6219,7 @@
         <v>372</v>
       </c>
       <c r="L319" s="7" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.4">
@@ -6227,7 +6227,7 @@
         <v>286</v>
       </c>
       <c r="L320" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.4">
@@ -6235,7 +6235,7 @@
         <v>287</v>
       </c>
       <c r="L321" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.4">
@@ -6243,7 +6243,7 @@
         <v>288</v>
       </c>
       <c r="L322" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.4">
@@ -6251,7 +6251,7 @@
         <v>289</v>
       </c>
       <c r="L323" s="7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.4">
@@ -6259,7 +6259,7 @@
         <v>290</v>
       </c>
       <c r="L324" s="7" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.4">
@@ -6267,7 +6267,7 @@
         <v>291</v>
       </c>
       <c r="L325" s="7" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.4">
@@ -6275,7 +6275,7 @@
         <v>292</v>
       </c>
       <c r="L326" s="7" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.4">
@@ -6283,7 +6283,7 @@
         <v>293</v>
       </c>
       <c r="L327" s="7" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.4">
@@ -6291,7 +6291,7 @@
         <v>294</v>
       </c>
       <c r="L328" s="7" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.4">
@@ -6299,7 +6299,7 @@
         <v>295</v>
       </c>
       <c r="L329" s="7" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.4">
@@ -6307,7 +6307,7 @@
         <v>296</v>
       </c>
       <c r="L330" s="7" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.4">
@@ -6315,7 +6315,7 @@
         <v>297</v>
       </c>
       <c r="L331" s="7" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.4">
@@ -6323,7 +6323,7 @@
         <v>298</v>
       </c>
       <c r="L332" s="7" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.4">
@@ -6331,7 +6331,7 @@
         <v>299</v>
       </c>
       <c r="L333" s="7" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.4">
@@ -6339,7 +6339,7 @@
         <v>300</v>
       </c>
       <c r="L334" s="7" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.4">
@@ -6347,7 +6347,7 @@
         <v>301</v>
       </c>
       <c r="L335" s="7" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.4">
@@ -6355,7 +6355,7 @@
         <v>302</v>
       </c>
       <c r="L336" s="7" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.4">
@@ -6363,7 +6363,7 @@
         <v>303</v>
       </c>
       <c r="L337" s="7" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="338" spans="1:12" x14ac:dyDescent="0.4">
@@ -6371,7 +6371,7 @@
         <v>304</v>
       </c>
       <c r="L338" s="7" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.4">
@@ -6379,7 +6379,7 @@
         <v>305</v>
       </c>
       <c r="L339" s="7" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.4">
@@ -6387,7 +6387,7 @@
         <v>306</v>
       </c>
       <c r="L340" s="7" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.4">
@@ -6395,7 +6395,7 @@
         <v>307</v>
       </c>
       <c r="L341" s="7" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.4">
@@ -6403,7 +6403,7 @@
         <v>308</v>
       </c>
       <c r="L342" s="7" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.4">
@@ -6411,7 +6411,7 @@
         <v>309</v>
       </c>
       <c r="L343" s="7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.4">
@@ -6419,7 +6419,7 @@
         <v>310</v>
       </c>
       <c r="L344" s="7" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.4">
@@ -6427,7 +6427,7 @@
         <v>311</v>
       </c>
       <c r="L345" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.4">
@@ -6435,7 +6435,7 @@
         <v>312</v>
       </c>
       <c r="L346" s="7" t="s">
-        <v>698</v>
+        <v>732</v>
       </c>
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.4">
@@ -6443,7 +6443,7 @@
         <v>313</v>
       </c>
       <c r="L347" s="7" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.4">
@@ -6451,39 +6451,39 @@
         <v>314</v>
       </c>
       <c r="L348" s="7" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="349" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="G349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="J349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="K349" s="8" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.4">
@@ -6491,7 +6491,7 @@
         <v>373</v>
       </c>
       <c r="L350" s="7" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.4">
@@ -6499,7 +6499,7 @@
         <v>315</v>
       </c>
       <c r="L351" s="7" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.4">
@@ -6507,7 +6507,7 @@
         <v>316</v>
       </c>
       <c r="L352" s="7" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.4">
@@ -6515,7 +6515,7 @@
         <v>317</v>
       </c>
       <c r="L353" s="7" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.4">
@@ -6523,7 +6523,7 @@
         <v>318</v>
       </c>
       <c r="L354" s="7" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.4">
@@ -6531,7 +6531,7 @@
         <v>319</v>
       </c>
       <c r="L355" s="7" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.4">
@@ -6539,7 +6539,7 @@
         <v>320</v>
       </c>
       <c r="L356" s="7" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.4">
@@ -6547,7 +6547,7 @@
         <v>321</v>
       </c>
       <c r="L357" s="7" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.4">
@@ -6555,7 +6555,7 @@
         <v>322</v>
       </c>
       <c r="L358" s="7" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.4">
@@ -6563,7 +6563,7 @@
         <v>323</v>
       </c>
       <c r="L359" s="7" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.4">
@@ -6571,7 +6571,7 @@
         <v>324</v>
       </c>
       <c r="L360" s="7" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.4">
@@ -6579,7 +6579,7 @@
         <v>325</v>
       </c>
       <c r="L361" s="7" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="362" spans="1:12" x14ac:dyDescent="0.4">
@@ -6587,7 +6587,7 @@
         <v>326</v>
       </c>
       <c r="L362" s="7" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.4">
@@ -6595,7 +6595,7 @@
         <v>327</v>
       </c>
       <c r="L363" s="7" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.4">
@@ -6603,7 +6603,7 @@
         <v>328</v>
       </c>
       <c r="L364" s="7" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.4">
@@ -6611,7 +6611,7 @@
         <v>329</v>
       </c>
       <c r="L365" s="7" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.4">
@@ -6619,7 +6619,7 @@
         <v>330</v>
       </c>
       <c r="L366" s="7" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.4">
@@ -6627,7 +6627,7 @@
         <v>331</v>
       </c>
       <c r="L367" s="7" t="s">
-        <v>718</v>
+        <v>731</v>
       </c>
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.4">
@@ -6635,7 +6635,7 @@
         <v>332</v>
       </c>
       <c r="L368" s="7" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.4">
@@ -6643,7 +6643,7 @@
         <v>333</v>
       </c>
       <c r="L369" s="7" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.4">
@@ -6651,7 +6651,7 @@
         <v>334</v>
       </c>
       <c r="L370" s="7" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.4">
@@ -6659,7 +6659,7 @@
         <v>335</v>
       </c>
       <c r="L371" s="7" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.4">
@@ -6667,7 +6667,7 @@
         <v>336</v>
       </c>
       <c r="L372" s="7" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.4">
@@ -6675,7 +6675,7 @@
         <v>337</v>
       </c>
       <c r="L373" s="7" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.4">
@@ -6683,7 +6683,7 @@
         <v>338</v>
       </c>
       <c r="L374" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.4">
@@ -6691,7 +6691,7 @@
         <v>339</v>
       </c>
       <c r="L375" s="7" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.4">
@@ -6699,7 +6699,7 @@
         <v>340</v>
       </c>
       <c r="L376" s="7" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.4">
@@ -6707,7 +6707,7 @@
         <v>341</v>
       </c>
       <c r="L377" s="7" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.4">
@@ -6715,7 +6715,7 @@
         <v>342</v>
       </c>
       <c r="L378" s="7" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.4">
@@ -6723,7 +6723,7 @@
         <v>343</v>
       </c>
       <c r="L379" s="7" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
     </row>
     <row r="380" spans="1:12" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
